--- a/src/xlsx/data.xlsx
+++ b/src/xlsx/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Sync/PokemonCHS/PKMN_G2/pokegoldCHS_build/pokegoldCHS/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Developer/Pokemon_Projects/pokegoldCHS/src/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C0634C-03E1-4146-A40B-7D2C4577A37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D4C195-2ABF-C143-90B4-95C09EE8FC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="5520" windowWidth="29400" windowHeight="17240" xr2:uid="{5D9A02DE-DD85-974B-B8A1-A92382739B9C}"/>
+    <workbookView xWindow="16320" yWindow="5520" windowWidth="29400" windowHeight="21780" xr2:uid="{5D9A02DE-DD85-974B-B8A1-A92382739B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Misc" sheetId="7" r:id="rId1"/>
@@ -4919,11 +4919,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>$69, "100      结束@"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"阿金@"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$69, "110      结束@"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5984,7 +5984,7 @@
         <v>82</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G49" t="s">
         <v>1</v>
@@ -11984,7 +11984,7 @@
         <v>862</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G568" t="s">
         <v>1</v>
@@ -12706,7 +12706,7 @@
         <v>862</v>
       </c>
       <c r="F627" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G627" t="s">
         <v>1</v>
